--- a/Data/Pertussis incidence.xlsx
+++ b/Data/Pertussis incidence.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="283" documentId="11_DAC534BE731DDAF072256778B06909E8BB729CDA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36FF6FC-E095-4F70-84C2-2BFC9293C259}"/>
   <bookViews>
-    <workbookView xWindow="2910" yWindow="3590" windowWidth="19420" windowHeight="12420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9280" yWindow="2090" windowWidth="28800" windowHeight="15460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Population" sheetId="11" r:id="rId1"/>
